--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -24,12 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-11-23</t>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
     <t>2025-11-25</t>
   </si>
   <si>
@@ -295,6 +289,9 @@
   </si>
   <si>
     <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
   </si>
   <si>
     <t>Issue</t>
@@ -353,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -375,7 +372,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +383,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +394,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +405,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +416,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +427,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="8">
@@ -474,7 +471,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +482,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="14">
@@ -518,7 +515,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +526,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +537,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +548,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +559,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +570,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +581,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +592,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +603,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="24">
@@ -650,7 +647,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +658,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="29">
@@ -694,7 +691,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +702,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +713,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +724,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +735,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +746,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="37">
@@ -782,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +790,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +801,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +812,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +823,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="45">
@@ -859,7 +856,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="47">
@@ -892,7 +889,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +900,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="52">
@@ -936,7 +933,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +944,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +955,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="56">
@@ -991,7 +988,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="59">
@@ -1013,7 +1010,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1021,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="62">
@@ -1046,7 +1043,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="64">
@@ -1068,7 +1065,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1076,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1087,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1098,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1109,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="70">
@@ -1189,7 +1186,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1197,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1208,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1219,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1230,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1241,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1252,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="83">
@@ -1277,7 +1274,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1285,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1296,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1307,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="88">
@@ -1343,7 +1340,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,17 +1351,6 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B92" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C92" t="n" s="0">
         <v>31.0</v>
       </c>
     </row>
@@ -1380,13 +1366,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,12 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
     <t>2025-11-27</t>
   </si>
   <si>
@@ -292,6 +286,12 @@
   </si>
   <si>
     <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
   </si>
   <si>
     <t>Issue</t>
@@ -372,7 +372,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="4">
@@ -394,7 +394,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -405,7 +405,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="6">
@@ -449,7 +449,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="10">
@@ -460,7 +460,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="11">
@@ -471,7 +471,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="12">
@@ -493,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="14">
@@ -504,7 +504,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="15">
@@ -515,7 +515,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="16">
@@ -526,7 +526,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="17">
@@ -537,7 +537,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="18">
@@ -548,7 +548,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="19">
@@ -559,7 +559,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="20">
@@ -570,7 +570,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +581,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="22">
@@ -625,7 +625,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +636,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="27">
@@ -669,7 +669,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="30">
@@ -680,7 +680,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="31">
@@ -691,7 +691,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="32">
@@ -702,7 +702,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="33">
@@ -713,7 +713,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="34">
@@ -724,7 +724,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="35">
@@ -757,7 +757,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="38">
@@ -768,7 +768,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="39">
@@ -779,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="40">
@@ -790,7 +790,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="41">
@@ -801,7 +801,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="42">
@@ -812,7 +812,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="43">
@@ -834,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="45">
@@ -867,7 +867,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="48">
@@ -878,7 +878,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="49">
@@ -889,7 +889,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="50">
@@ -911,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="52">
@@ -922,7 +922,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="53">
@@ -933,7 +933,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="54">
@@ -966,7 +966,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="57">
@@ -988,7 +988,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +999,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="60">
@@ -1021,7 +1021,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="62">
@@ -1043,7 +1043,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="64">
@@ -1054,7 +1054,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1065,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="66">
@@ -1076,7 +1076,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="67">
@@ -1087,7 +1087,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="68">
@@ -1164,7 +1164,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="75">
@@ -1175,7 +1175,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="76">
@@ -1186,7 +1186,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="77">
@@ -1197,7 +1197,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="78">
@@ -1208,7 +1208,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="79">
@@ -1219,7 +1219,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="80">
@@ -1230,7 +1230,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="81">
@@ -1252,7 +1252,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="83">
@@ -1263,7 +1263,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="84">
@@ -1274,7 +1274,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="85">
@@ -1285,7 +1285,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="86">
@@ -1318,7 +1318,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="89">
@@ -1329,7 +1329,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="90">

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -24,9 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
     <t>2025-11-28</t>
   </si>
   <si>
@@ -292,6 +289,12 @@
   </si>
   <si>
     <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
   </si>
   <si>
     <t>Issue</t>
@@ -350,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -383,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
@@ -438,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="9">
@@ -449,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="10">
@@ -482,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="13">
@@ -493,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="14">
@@ -515,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="16">
@@ -537,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="18">
@@ -559,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="20">
@@ -614,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="25">
@@ -658,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="29">
@@ -669,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="30">
@@ -680,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="31">
@@ -691,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="32">
@@ -702,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="33">
@@ -746,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="37">
@@ -768,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="39">
@@ -779,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="40">
@@ -801,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="42">
@@ -812,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="43">
@@ -856,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="47">
@@ -878,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="49">
@@ -889,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="50">
@@ -911,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="52">
@@ -955,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="56">
@@ -966,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="57">
@@ -977,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="58">
@@ -988,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="60">
@@ -1032,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="63">
@@ -1043,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="64">
@@ -1054,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="66">
@@ -1153,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="74">
@@ -1175,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="76">
@@ -1186,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="77">
@@ -1208,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="79">
@@ -1241,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="82">
@@ -1263,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="84">
@@ -1307,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="88">
@@ -1351,7 +1354,18 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C92" t="n" s="0">
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -1366,13 +1380,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,9 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
     <t>2025-11-29</t>
   </si>
   <si>
@@ -295,6 +292,9 @@
   </si>
   <si>
     <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="3">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="9">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="13">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="15">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="17">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="19">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="24">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="32">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="36">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="39">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="42">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="46">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="49">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="51">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="59">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="65">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="73">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="76">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="78">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="81">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="83">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="87">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="92">

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -22,9 +22,6 @@
   </si>
   <si>
     <t>HTTPS URLs</t>
-  </si>
-  <si>
-    <t>2025-11-29</t>
   </si>
   <si>
     <t>2025-11-30</t>
@@ -353,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -419,7 +416,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +427,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="8">
@@ -463,7 +460,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +471,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="12">
@@ -496,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="14">
@@ -518,7 +515,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="16">
@@ -540,7 +537,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="18">
@@ -595,7 +592,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="23">
@@ -639,7 +636,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +647,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +658,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +669,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +680,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="31">
@@ -727,7 +724,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="35">
@@ -749,7 +746,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +757,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="38">
@@ -782,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +790,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="41">
@@ -837,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="45">
@@ -859,7 +856,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +867,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="48">
@@ -892,7 +889,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="50">
@@ -936,7 +933,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +944,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +955,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +966,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="58">
@@ -1013,7 +1010,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1021,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1032,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1043,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="64">
@@ -1134,7 +1131,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="72">
@@ -1156,7 +1153,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1164,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="75">
@@ -1189,7 +1186,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="77">
@@ -1222,7 +1219,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="80">
@@ -1244,7 +1241,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="82">
@@ -1288,7 +1285,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="86">
@@ -1332,7 +1329,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1340,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,17 +1351,6 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>33.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B92" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C92" t="n" s="0">
         <v>33.0</v>
       </c>
     </row>
@@ -1380,13 +1366,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,12 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-11-30</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
     <t>2025-12-02</t>
   </si>
   <si>
@@ -292,6 +286,12 @@
   </si>
   <si>
     <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
   </si>
   <si>
     <t>Issue</t>
@@ -394,7 +394,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="5">
@@ -405,7 +405,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="6">
@@ -416,7 +416,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="7">
@@ -438,7 +438,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="9">
@@ -449,7 +449,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="10">
@@ -460,7 +460,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="11">
@@ -471,7 +471,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="12">
@@ -482,7 +482,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="13">
@@ -493,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="14">
@@ -504,7 +504,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="15">
@@ -515,7 +515,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="16">
@@ -526,7 +526,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="17">
@@ -570,7 +570,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +581,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="22">
@@ -614,7 +614,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="25">
@@ -625,7 +625,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +636,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="27">
@@ -647,7 +647,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -658,7 +658,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="29">
@@ -669,7 +669,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="30">
@@ -702,7 +702,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="33">
@@ -713,7 +713,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="34">
@@ -724,7 +724,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="35">
@@ -735,7 +735,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="36">
@@ -746,7 +746,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="37">
@@ -757,7 +757,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="38">
@@ -779,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="40">
@@ -812,7 +812,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="43">
@@ -823,7 +823,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="44">
@@ -834,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="45">
@@ -856,7 +856,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="47">
@@ -867,7 +867,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="48">
@@ -878,7 +878,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="49">
@@ -911,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="52">
@@ -933,7 +933,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="54">
@@ -944,7 +944,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="55">
@@ -966,7 +966,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="57">
@@ -988,7 +988,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +999,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="60">
@@ -1010,7 +1010,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="61">
@@ -1021,7 +1021,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="62">
@@ -1032,7 +1032,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="63">
@@ -1109,7 +1109,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="70">
@@ -1120,7 +1120,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="71">
@@ -1131,7 +1131,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="72">
@@ -1142,7 +1142,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="73">
@@ -1153,7 +1153,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="74">
@@ -1164,7 +1164,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="75">
@@ -1175,7 +1175,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="76">
@@ -1197,7 +1197,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="78">
@@ -1208,7 +1208,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="79">
@@ -1219,7 +1219,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="80">
@@ -1230,7 +1230,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="81">
@@ -1263,7 +1263,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="84">
@@ -1274,7 +1274,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="85">
@@ -1307,7 +1307,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="88">
@@ -1318,7 +1318,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="89">
@@ -1329,7 +1329,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="90">
@@ -1340,7 +1340,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="91">
@@ -1351,7 +1351,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,9 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-12-02</t>
-  </si>
-  <si>
     <t>2025-12-03</t>
   </si>
   <si>
@@ -292,6 +289,9 @@
   </si>
   <si>
     <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
   </si>
   <si>
     <t>Issue</t>
@@ -383,7 +383,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
@@ -394,7 +394,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="5">
@@ -427,7 +427,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="8">
@@ -438,7 +438,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="9">
@@ -460,7 +460,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
@@ -482,7 +482,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="13">
@@ -504,7 +504,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="15">
@@ -559,7 +559,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="20">
@@ -603,7 +603,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="24">
@@ -614,7 +614,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="25">
@@ -625,7 +625,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +636,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="27">
@@ -647,7 +647,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="28">
@@ -691,7 +691,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="32">
@@ -713,7 +713,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="34">
@@ -724,7 +724,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="35">
@@ -746,7 +746,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="37">
@@ -757,7 +757,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="38">
@@ -801,7 +801,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="42">
@@ -823,7 +823,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="44">
@@ -834,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="45">
@@ -856,7 +856,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="47">
@@ -900,7 +900,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="51">
@@ -911,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="52">
@@ -922,7 +922,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="53">
@@ -933,7 +933,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="54">
@@ -944,7 +944,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="55">
@@ -977,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="58">
@@ -988,7 +988,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +999,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="60">
@@ -1010,7 +1010,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="61">
@@ -1098,7 +1098,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="69">
@@ -1120,7 +1120,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="71">
@@ -1131,7 +1131,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="72">
@@ -1153,7 +1153,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="74">
@@ -1186,7 +1186,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="77">
@@ -1208,7 +1208,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="79">
@@ -1252,7 +1252,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="83">
@@ -1296,7 +1296,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="87">
@@ -1307,7 +1307,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="88">
@@ -1329,7 +1329,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="90">
@@ -1351,7 +1351,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -24,9 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
     <t>2025-12-04</t>
   </si>
   <si>
@@ -292,6 +289,12 @@
   </si>
   <si>
     <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
   </si>
   <si>
     <t>Issue</t>
@@ -350,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -372,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="4">
@@ -416,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="7">
@@ -427,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="8">
@@ -449,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="10">
@@ -471,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="12">
@@ -493,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="19">
@@ -592,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="23">
@@ -603,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="24">
@@ -614,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="25">
@@ -625,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="27">
@@ -680,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="31">
@@ -702,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="33">
@@ -713,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="34">
@@ -735,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="36">
@@ -746,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="37">
@@ -790,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="41">
@@ -812,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="43">
@@ -823,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="44">
@@ -845,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="46">
@@ -889,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="50">
@@ -900,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="51">
@@ -911,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="52">
@@ -922,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="53">
@@ -933,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="54">
@@ -966,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="57">
@@ -977,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="58">
@@ -988,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="60">
@@ -1087,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="68">
@@ -1109,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="70">
@@ -1120,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="71">
@@ -1142,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="73">
@@ -1175,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="76">
@@ -1197,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="78">
@@ -1241,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="82">
@@ -1285,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="86">
@@ -1296,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="87">
@@ -1318,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="89">
@@ -1340,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="91">
@@ -1351,6 +1354,17 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C92" t="n" s="0">
         <v>35.0</v>
       </c>
     </row>
@@ -1366,13 +1380,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -24,12 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-12-04</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
     <t>2025-12-06</t>
   </si>
   <si>
@@ -295,6 +289,9 @@
   </si>
   <si>
     <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
   </si>
   <si>
     <t>Issue</t>
@@ -353,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -375,7 +372,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +394,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +405,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +416,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +427,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +438,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +449,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +460,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +471,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +482,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="13">
@@ -529,7 +526,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +537,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +570,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +581,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +592,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +603,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +614,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +625,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="26">
@@ -661,7 +658,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +669,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +680,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +691,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +702,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +713,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="34">
@@ -738,7 +735,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="36">
@@ -771,7 +768,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +790,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="41">
@@ -815,7 +812,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +823,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="45">
@@ -870,7 +867,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="48">
@@ -892,7 +889,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +900,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="51">
@@ -925,7 +922,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="53">
@@ -947,7 +944,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +955,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +966,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +988,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="59">
@@ -1068,7 +1065,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1076,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1087,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1098,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1109,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1120,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1131,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="72">
@@ -1156,7 +1153,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1164,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1175,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1186,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="77">
@@ -1222,7 +1219,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1230,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="81">
@@ -1266,7 +1263,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1274,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1285,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1296,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1307,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1318,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1329,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="90">
@@ -1354,17 +1351,6 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B92" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C92" t="n" s="0">
         <v>35.0</v>
       </c>
     </row>
@@ -1380,13 +1366,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -24,36 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-12-06</t>
-  </si>
-  <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
     <t>2025-12-16</t>
   </si>
   <si>
@@ -292,6 +262,39 @@
   </si>
   <si>
     <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
   </si>
   <si>
     <t>Issue</t>
@@ -350,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -372,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="4">
@@ -394,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
@@ -405,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="6">
@@ -416,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="7">
@@ -427,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="8">
@@ -438,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="9">
@@ -449,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="10">
@@ -482,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="13">
@@ -493,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="14">
@@ -504,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="15">
@@ -515,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="16">
@@ -526,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="17">
@@ -537,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="18">
@@ -548,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="19">
@@ -559,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="20">
@@ -570,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="22">
@@ -592,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="23">
@@ -603,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="24">
@@ -614,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="25">
@@ -625,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="27">
@@ -647,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="28">
@@ -658,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="29">
@@ -669,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="30">
@@ -680,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="31">
@@ -691,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="32">
@@ -702,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="33">
@@ -713,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="34">
@@ -724,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="35">
@@ -735,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="36">
@@ -746,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="37">
@@ -757,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="38">
@@ -768,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="39">
@@ -779,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="40">
@@ -790,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>27.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="41">
@@ -801,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="42">
@@ -812,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="43">
@@ -823,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="44">
@@ -845,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="46">
@@ -856,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="47">
@@ -867,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="48">
@@ -878,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="49">
@@ -889,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="50">
@@ -900,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="51">
@@ -911,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="52">
@@ -922,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="53">
@@ -933,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="54">
@@ -944,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="55">
@@ -955,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="56">
@@ -988,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="60">
@@ -1010,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="61">
@@ -1021,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="62">
@@ -1032,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="63">
@@ -1043,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="64">
@@ -1054,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="66">
@@ -1076,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="67">
@@ -1087,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="68">
@@ -1098,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="69">
@@ -1109,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="70">
@@ -1120,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="71">
@@ -1131,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="72">
@@ -1142,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="73">
@@ -1153,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="74">
@@ -1164,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="75">
@@ -1175,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="76">
@@ -1186,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="77">
@@ -1197,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="78">
@@ -1208,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="79">
@@ -1219,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="80">
@@ -1230,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="81">
@@ -1241,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="82">
@@ -1252,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="83">
@@ -1263,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="84">
@@ -1274,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="85">
@@ -1285,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="86">
@@ -1296,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="87">
@@ -1307,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="88">
@@ -1318,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="89">
@@ -1329,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="90">
@@ -1340,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="91">
@@ -1351,7 +1354,18 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C92" t="n" s="0">
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>
@@ -1366,13 +1380,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,69 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
     <t>2026-01-06</t>
   </si>
   <si>
@@ -295,6 +232,69 @@
   </si>
   <si>
     <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>30.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>31.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>32.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>29.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="25">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>24.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>24.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>27.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>27.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="70">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>33.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>33.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>33.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="91">

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,21 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
     <t>2026-01-11</t>
   </si>
   <si>
@@ -295,6 +280,21 @@
   </si>
   <si>
     <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="11">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="26">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="31">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="39">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="43">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="57">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="63">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="75">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="88">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="92">

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,45 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
     <t>2026-01-24</t>
   </si>
   <si>
@@ -295,6 +256,45 @@
   </si>
   <si>
     <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="6">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="48">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="86">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,81 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-01-31</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
     <t>2026-02-18</t>
   </si>
   <si>
@@ -295,6 +220,81 @@
   </si>
   <si>
     <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>27.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>27.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>33.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="54">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>30.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>32.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>32.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>32.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>31.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>32.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>32.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>33.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>33.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>35.0</v>
+        <v>46.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,42 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>2026-02-21</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
     <t>2026-03-02</t>
   </si>
   <si>
@@ -295,6 +259,42 @@
   </si>
   <si>
     <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="9">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="49">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>35.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>34.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>36.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>37.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>37.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>37.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>39.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>42.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>42.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>46.0</v>
+        <v>45.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,21 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>2026-03-03</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
     <t>2026-03-07</t>
   </si>
   <si>
@@ -295,6 +280,21 @@
   </si>
   <si>
     <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
   </si>
   <si>
     <t>Issue</t>
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="8">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="20">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="33">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="37">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="43">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="46">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="64">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="81">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>47.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="89">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,30 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-03-07</t>
-  </si>
-  <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
     <t>2026-03-15</t>
   </si>
   <si>
@@ -295,6 +271,30 @@
   </si>
   <si>
     <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>33.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>33.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="17">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="26">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="28">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="38">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>39.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="82">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,36 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>2026-03-22</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
     <t>2026-03-25</t>
   </si>
   <si>
@@ -295,6 +265,36 @@
   </si>
   <si>
     <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="6">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="8">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="17">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>36.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>37.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>39.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="72">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>49.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
     <t>2026-03-31</t>
   </si>
   <si>
@@ -295,6 +277,24 @@
   </si>
   <si>
     <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="9">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="12">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="41">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="58">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="65">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="72">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
     <t>2026-04-06</t>
   </si>
   <si>
@@ -295,6 +277,21 @@
   </si>
   <si>
     <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
   </si>
   <si>
     <t>Issue</t>
@@ -353,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -375,7 +372,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +394,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +405,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="6">
@@ -441,7 +438,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +449,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +460,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +471,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +482,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +504,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +515,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="16">
@@ -551,7 +548,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +559,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +570,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +581,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +592,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +603,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +614,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +625,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +636,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +647,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +658,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +669,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +680,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +691,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +702,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +713,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +724,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="35">
@@ -749,7 +746,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +757,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +768,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +790,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +801,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +812,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +823,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +845,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +856,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +867,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +878,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +889,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +900,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="52">
@@ -936,7 +933,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +944,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +955,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +966,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +988,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="59">
@@ -1013,7 +1010,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1021,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1032,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1043,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1054,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1065,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="66">
@@ -1101,7 +1098,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1109,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1120,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1131,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1142,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1153,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1164,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1175,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1186,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1197,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1208,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1219,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1230,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1241,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1252,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1263,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1274,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1285,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1296,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1307,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1318,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1329,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1340,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,18 +1351,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>65.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B92" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C92" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
   </sheetData>
@@ -1380,13 +1366,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
     <t>2026-04-12</t>
   </si>
   <si>
@@ -292,6 +274,27 @@
   </si>
   <si>
     <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
   </si>
   <si>
     <t>Issue</t>
@@ -350,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -372,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -394,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="5">
@@ -405,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="6">
@@ -416,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="7">
@@ -427,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="8">
@@ -438,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="9">
@@ -449,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="10">
@@ -482,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="13">
@@ -493,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="14">
@@ -504,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="15">
@@ -515,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="16">
@@ -526,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="17">
@@ -537,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="18">
@@ -548,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="19">
@@ -559,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="20">
@@ -570,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="22">
@@ -592,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="23">
@@ -603,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="24">
@@ -614,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="25">
@@ -625,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="27">
@@ -647,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="28">
@@ -658,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="29">
@@ -680,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="31">
@@ -691,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="32">
@@ -702,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="33">
@@ -713,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="34">
@@ -724,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="35">
@@ -735,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="36">
@@ -746,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="37">
@@ -757,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="38">
@@ -768,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="39">
@@ -779,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="40">
@@ -790,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="41">
@@ -801,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="42">
@@ -812,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="43">
@@ -823,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="44">
@@ -834,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="45">
@@ -845,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="46">
@@ -867,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="48">
@@ -878,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="49">
@@ -889,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="50">
@@ -900,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="51">
@@ -911,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="52">
@@ -922,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="53">
@@ -944,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="55">
@@ -955,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="56">
@@ -966,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="57">
@@ -977,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="58">
@@ -988,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="60">
@@ -1032,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="63">
@@ -1043,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="64">
@@ -1054,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="66">
@@ -1076,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="67">
@@ -1087,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="68">
@@ -1098,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1109,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1120,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="71">
@@ -1131,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="72">
@@ -1142,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="73">
@@ -1153,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="74">
@@ -1164,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="75">
@@ -1175,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="76">
@@ -1186,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="77">
@@ -1197,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="78">
@@ -1208,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="79">
@@ -1219,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="80">
@@ -1230,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="81">
@@ -1241,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="82">
@@ -1252,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="83">
@@ -1263,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="84">
@@ -1274,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="85">
@@ -1285,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="86">
@@ -1307,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="88">
@@ -1318,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="89">
@@ -1329,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="90">
@@ -1340,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="91">
@@ -1351,7 +1354,18 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C92" t="n" s="0">
+        <v>67.0</v>
       </c>
     </row>
   </sheetData>
@@ -1366,13 +1380,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,30 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
     <t>2026-04-20</t>
   </si>
   <si>
@@ -295,6 +271,30 @@
   </si>
   <si>
     <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
   </si>
   <si>
     <t>Issue</t>
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>39.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="46">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>60.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="79">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="81">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
     <t>2026-04-26</t>
   </si>
   <si>
@@ -295,6 +277,24 @@
   </si>
   <si>
     <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="15">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="32">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="39">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="46">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="72">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,33 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
     <t>2026-05-05</t>
   </si>
   <si>
@@ -295,6 +268,33 @@
   </si>
   <si>
     <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>39.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="31">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="39">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="84">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,30 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
     <t>2026-05-13</t>
   </si>
   <si>
@@ -295,6 +271,30 @@
   </si>
   <si>
     <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>39.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="23">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>60.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="56">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="58">
@@ -1002,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1244,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="92">

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
     <t>2026-05-19</t>
   </si>
   <si>
@@ -295,6 +277,21 @@
   </si>
   <si>
     <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
   </si>
   <si>
     <t>Issue</t>
@@ -353,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -375,7 +372,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +383,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +394,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +405,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +416,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +427,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +438,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="9">
@@ -463,7 +460,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +471,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +482,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +504,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +515,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="16">
@@ -540,7 +537,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +548,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +559,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +570,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +581,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +592,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="23">
@@ -628,7 +625,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +636,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +647,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +658,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +669,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +680,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +691,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +702,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +713,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +724,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +735,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +746,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +757,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +768,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +790,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +801,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +812,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +823,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +845,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +856,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +867,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +878,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="49">
@@ -903,7 +900,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +911,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +922,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +933,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +944,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +955,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="56">
@@ -969,7 +966,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +988,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +999,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1010,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1021,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1032,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1043,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1054,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1065,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1076,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1087,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1098,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1109,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1120,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1131,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1142,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1153,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1164,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1175,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1186,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1197,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1208,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1219,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1230,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1241,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1252,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1263,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="84">
@@ -1354,18 +1351,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>57.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B92" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C92" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
   </sheetData>
@@ -1380,13 +1366,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-23</t>
-  </si>
-  <si>
-    <t>2026-05-24</t>
-  </si>
-  <si>
     <t>2026-05-25</t>
   </si>
   <si>
@@ -292,6 +274,27 @@
   </si>
   <si>
     <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
   </si>
   <si>
     <t>Issue</t>
@@ -350,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -372,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="3">
@@ -394,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="5">
@@ -405,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="6">
@@ -416,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="7">
@@ -427,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="8">
@@ -438,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="9">
@@ -449,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="10">
@@ -471,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="12">
@@ -482,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="13">
@@ -493,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="14">
@@ -504,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="15">
@@ -515,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="16">
@@ -526,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="17">
@@ -559,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="20">
@@ -570,7 +573,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="22">
@@ -592,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="23">
@@ -603,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="24">
@@ -614,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="25">
@@ -625,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="27">
@@ -647,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="28">
@@ -658,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="29">
@@ -669,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="30">
@@ -680,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="31">
@@ -691,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="32">
@@ -702,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="33">
@@ -713,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="34">
@@ -724,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="35">
@@ -735,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="36">
@@ -746,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="37">
@@ -757,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="38">
@@ -768,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="39">
@@ -779,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="40">
@@ -790,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="41">
@@ -801,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="42">
@@ -812,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="43">
@@ -834,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="45">
@@ -845,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="46">
@@ -856,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="47">
@@ -867,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="48">
@@ -878,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="49">
@@ -889,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="50">
@@ -900,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="51">
@@ -911,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="52">
@@ -922,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="53">
@@ -933,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="54">
@@ -944,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="55">
@@ -955,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="56">
@@ -966,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="57">
@@ -977,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="58">
@@ -988,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="59">
@@ -999,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="60">
@@ -1010,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="61">
@@ -1021,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="62">
@@ -1032,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="63">
@@ -1043,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="64">
@@ -1054,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="66">
@@ -1076,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="67">
@@ -1087,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="68">
@@ -1098,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="69">
@@ -1109,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="70">
@@ -1120,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="71">
@@ -1131,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="72">
@@ -1142,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="73">
@@ -1153,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="74">
@@ -1164,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="75">
@@ -1175,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="76">
@@ -1186,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="77">
@@ -1197,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="78">
@@ -1285,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="86">
@@ -1296,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="87">
@@ -1307,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="88">
@@ -1318,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="89">
@@ -1329,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="90">
@@ -1340,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="91">
@@ -1351,7 +1354,18 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C92" t="n" s="0">
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>
@@ -1366,13 +1380,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -24,33 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
     <t>2026-06-03</t>
   </si>
   <si>
@@ -295,6 +268,27 @@
   </si>
   <si>
     <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
   </si>
   <si>
     <t>Issue</t>
@@ -353,7 +347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -397,7 +391,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +402,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +413,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +424,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +435,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +446,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="10">
@@ -474,7 +468,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +479,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +490,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="14">
@@ -507,7 +501,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="15">
@@ -518,7 +512,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="16">
@@ -529,7 +523,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +534,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="18">
@@ -551,7 +545,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="19">
@@ -562,7 +556,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +567,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="21">
@@ -584,7 +578,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="22">
@@ -595,7 +589,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +600,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +611,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +622,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +633,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +644,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +655,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +666,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +688,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +699,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="33">
@@ -716,7 +710,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="34">
@@ -727,7 +721,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="35">
@@ -738,7 +732,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +743,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +754,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="38">
@@ -771,7 +765,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +776,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="40">
@@ -793,7 +787,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="41">
@@ -804,7 +798,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +809,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="43">
@@ -826,7 +820,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="44">
@@ -837,7 +831,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="45">
@@ -848,7 +842,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +853,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +864,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="48">
@@ -881,7 +875,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +886,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="50">
@@ -903,7 +897,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="51">
@@ -914,7 +908,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="52">
@@ -925,7 +919,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="53">
@@ -936,7 +930,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +941,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="55">
@@ -969,7 +963,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +974,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="58">
@@ -991,7 +985,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="59">
@@ -1002,7 +996,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1007,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="61">
@@ -1024,7 +1018,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1029,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1040,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1051,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="65">
@@ -1068,7 +1062,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1073,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="67">
@@ -1090,7 +1084,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1095,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="69">
@@ -1112,7 +1106,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="70">
@@ -1123,7 +1117,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1128,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="72">
@@ -1189,7 +1183,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1194,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1205,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="79">
@@ -1222,7 +1216,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="80">
@@ -1233,7 +1227,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="81">
@@ -1244,7 +1238,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1249,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="83">
@@ -1266,7 +1260,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="84">
@@ -1277,7 +1271,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="85">
@@ -1288,7 +1282,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="86">
@@ -1299,7 +1293,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="87">
@@ -1310,7 +1304,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1315,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1326,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="90">
@@ -1344,28 +1338,6 @@
       </c>
       <c r="C90" t="n" s="0">
         <v>53.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>52.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B92" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C92" t="n" s="0">
-        <v>52.0</v>
       </c>
     </row>
   </sheetData>
@@ -1380,13 +1352,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,33 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>2026-06-07</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
     <t>2026-06-12</t>
   </si>
   <si>
@@ -289,6 +262,33 @@
   </si>
   <si>
     <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>Issue</t>
@@ -369,7 +369,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="3">
@@ -380,7 +380,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="4">
@@ -391,7 +391,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="5">
@@ -402,7 +402,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="6">
@@ -413,7 +413,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="7">
@@ -424,7 +424,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="8">
@@ -435,7 +435,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="9">
@@ -446,7 +446,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="10">
@@ -457,7 +457,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="11">
@@ -468,7 +468,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="12">
@@ -479,7 +479,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="13">
@@ -490,7 +490,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="14">
@@ -501,7 +501,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="15">
@@ -512,7 +512,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="16">
@@ -523,7 +523,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="17">
@@ -534,7 +534,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="18">
@@ -545,7 +545,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="19">
@@ -556,7 +556,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="20">
@@ -567,7 +567,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="21">
@@ -578,7 +578,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="22">
@@ -589,7 +589,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="23">
@@ -600,7 +600,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="24">
@@ -611,7 +611,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="25">
@@ -622,7 +622,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="26">
@@ -633,7 +633,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="27">
@@ -644,7 +644,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="28">
@@ -655,7 +655,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="29">
@@ -666,7 +666,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="30">
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="31">
@@ -688,7 +688,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="32">
@@ -699,7 +699,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="33">
@@ -710,7 +710,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="34">
@@ -721,7 +721,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="35">
@@ -732,7 +732,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="36">
@@ -743,7 +743,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="37">
@@ -754,7 +754,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="38">
@@ -765,7 +765,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="39">
@@ -776,7 +776,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="40">
@@ -787,7 +787,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="41">
@@ -798,7 +798,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="42">
@@ -809,7 +809,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="43">
@@ -820,7 +820,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="44">
@@ -831,7 +831,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="45">
@@ -842,7 +842,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="46">
@@ -864,7 +864,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="48">
@@ -875,7 +875,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="49">
@@ -886,7 +886,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="50">
@@ -897,7 +897,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="51">
@@ -908,7 +908,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="52">
@@ -919,7 +919,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="53">
@@ -930,7 +930,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="54">
@@ -941,7 +941,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="55">
@@ -952,7 +952,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="56">
@@ -963,7 +963,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="57">
@@ -974,7 +974,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="58">
@@ -985,7 +985,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="59">
@@ -996,7 +996,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="60">
@@ -1007,7 +1007,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="61">
@@ -1018,7 +1018,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="62">
@@ -1029,7 +1029,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="63">
@@ -1084,7 +1084,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="68">
@@ -1095,7 +1095,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1106,7 +1106,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1117,7 +1117,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="71">
@@ -1128,7 +1128,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="72">
@@ -1139,7 +1139,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="73">
@@ -1150,7 +1150,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="74">
@@ -1161,7 +1161,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="75">
@@ -1172,7 +1172,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="76">
@@ -1183,7 +1183,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="77">
@@ -1194,7 +1194,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="78">
@@ -1205,7 +1205,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="79">
@@ -1216,7 +1216,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="80">
@@ -1227,7 +1227,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="81">
@@ -1249,7 +1249,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="83">
@@ -1260,7 +1260,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="84">
@@ -1271,7 +1271,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="85">
@@ -1282,7 +1282,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="86">
@@ -1293,7 +1293,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="87">
@@ -1304,7 +1304,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="88">
@@ -1337,7 +1337,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
   </sheetData>
